--- a/output/pdf_financials_xlsx/GLDN.xlsx
+++ b/output/pdf_financials_xlsx/GLDN.xlsx
@@ -6733,31 +6733,31 @@
         <v>0.11933</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.186987</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>-0.16325</v>
+        <v>-1.886684</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.015591</v>
+        <v>-3.185613</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>-0.0375</v>
+        <v>-2.125798</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>6.681786</v>
+        <v>5.463326</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.75989</v>
+        <v>0.1444</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>2.466514</v>
+        <v>0.549414</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>-0.12</v>
+        <v>-1.098289</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.455005</v>
       </c>
     </row>
     <row r="119">
@@ -12544,7 +12544,11 @@
           <t>Prepaids and deposit</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -18202,7 +18206,11 @@
           <t>Recovery of exploration and evaluation expenditures 10</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -19149,7 +19157,11 @@
           <t>Recovery of exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -19325,7 +19337,11 @@
           <t>Exploration and evaluation asset expenditures 10</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -20937,7 +20953,11 @@
           <t>Recovery of exploration and evaluation asset expenditures 9</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -21107,7 +21127,11 @@
           <t>Exploration and evaluation asset expenditures 9</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -22531,7 +22555,11 @@
           <t>Exploration and evaluation asset expenditures 9</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -26234,7 +26262,11 @@
           <t>Recovery of exploration and evaluation asset expenditures 9</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -26325,7 +26357,11 @@
           <t>Exploration and evaluation asset expenditures 9</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -29902,7 +29938,11 @@
           <t>Exploration and evaluation asset expenditures 9</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GLDN.xlsx
+++ b/output/pdf_financials_xlsx/GLDN.xlsx
@@ -911,31 +911,31 @@
         <v>0.196104</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.240137</v>
+        <v>0.054301</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>1.498227</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>1.035654</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.610725</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>0.798451</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>1.239741</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.410094</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.7218830000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.965494</v>
       </c>
     </row>
     <row r="11">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0</v>
+        <v>-0.7218830000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>-0.965494</v>
       </c>
     </row>
     <row r="12">
@@ -1027,31 +1027,31 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>9.2e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.021901</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.029524</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.007579</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.024179</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.099048</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.057721</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.03288</v>
       </c>
     </row>
     <row r="13">
@@ -1893,31 +1893,31 @@
         <v>-0.355294</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.054209</v>
+        <v>-0.054301</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.010458</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.765629</v>
+        <v>-0.78753</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.521477</v>
+        <v>-0.551001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-7.341336</v>
+        <v>-7.348915</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.700774</v>
+        <v>-1.724953</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.758112</v>
+        <v>-2.85716</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.545557</v>
+        <v>-0.603278</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.493217</v>
+        <v>-0.526097</v>
       </c>
     </row>
     <row r="28">
@@ -1997,31 +1997,31 @@
         <v>-0.355294</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.054209</v>
+        <v>-0.054301</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.001719</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.742344</v>
+        <v>-0.764245</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.498574</v>
+        <v>-0.528098</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.314565</v>
+        <v>-7.322144</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.667616</v>
+        <v>-1.691795</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.731604</v>
+        <v>-2.830652</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.530938</v>
+        <v>-0.588659</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.470344</v>
+        <v>-0.503224</v>
       </c>
     </row>
     <row r="30">
@@ -2254,22 +2254,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.428987</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.303887</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.080153</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.242662</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.00618</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.00685</v>
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.428987</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.303887</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.080153</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.242662</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.00618</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.00685</v>
@@ -2982,22 +2982,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.428987</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.299262</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.08665299999999999</v>
+        <v>0.0065</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.266487</v>
+        <v>0.023825</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.00618</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.003057</v>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -37163,7 +37163,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -37197,31 +37197,31 @@
         </is>
       </c>
       <c r="K326" s="5" t="n">
-        <v>-0.054301</v>
+        <v>0.054301</v>
       </c>
       <c r="L326" s="5" t="n">
-        <v>-1.498227</v>
+        <v>1.498227</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>-1.035654</v>
+        <v>1.035654</v>
       </c>
       <c r="N326" s="5" t="n">
-        <v>-0.610725</v>
+        <v>0.610725</v>
       </c>
       <c r="O326" s="5" t="n">
-        <v>-0.798451</v>
+        <v>0.798451</v>
       </c>
       <c r="P326" s="5" t="n">
-        <v>-1.239741</v>
+        <v>1.239741</v>
       </c>
       <c r="Q326" s="5" t="n">
-        <v>-0.410094</v>
+        <v>0.410094</v>
       </c>
       <c r="R326" s="5" t="n">
-        <v>-0.7218830000000001</v>
+        <v>0.7218830000000001</v>
       </c>
       <c r="S326" s="5" t="n">
-        <v>-0.965494</v>
+        <v>0.965494</v>
       </c>
     </row>
     <row r="327">
@@ -37242,7 +37242,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -37424,7 +37424,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -38496,7 +38496,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -42274,7 +42274,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">

--- a/output/pdf_financials_xlsx/GLDN.xlsx
+++ b/output/pdf_financials_xlsx/GLDN.xlsx
@@ -767,19 +767,19 @@
         <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="8">
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000201</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.018361</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0.013937</v>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.002495</v>
+        <v>0.002294</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.068282</v>
+        <v>0.049921</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.045432</v>
@@ -6381,19 +6381,19 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.036516</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09551800000000001</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.121878</v>
       </c>
     </row>
     <row r="112">
@@ -6546,10 +6546,10 @@
         <v>0</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-0.049814</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0</v>
+        <v>-0.865892</v>
       </c>
     </row>
     <row r="115">
@@ -6586,10 +6586,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.055086</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.017352</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -6598,10 +6598,10 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.063761</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>1.55253</v>
       </c>
     </row>
     <row r="116">
@@ -7611,19 +7611,19 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.036516</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09551800000000001</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.121878</v>
       </c>
     </row>
     <row r="135">
@@ -7663,19 +7663,19 @@
         <v>-0.198839</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.754365</v>
+        <v>-0.781365</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>0.11477</v>
+        <v>0.078254</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.401516</v>
+        <v>-0.402516</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-0.293876</v>
+        <v>-0.389394</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.046718</v>
+        <v>-1.168596</v>
       </c>
     </row>
   </sheetData>
@@ -18979,7 +18979,11 @@
           <t>Proceeds from the sale of marketable securities 8</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -19068,7 +19072,11 @@
           <t>Purchase of marketable securities 8</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -19248,7 +19256,11 @@
           <t>Purchase of equipment 9</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -20771,7 +20783,11 @@
           <t>Proceeds from the sale of marketable securities 7</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -20862,7 +20878,11 @@
           <t>Purchase of marketable securities 7</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -21042,7 +21062,11 @@
           <t>Purchase of equipment 8</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -22466,7 +22490,11 @@
           <t>Purchase of equipment 8</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -22832,7 +22860,11 @@
           <t>Shares issued for private placement 10</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -24023,7 +24055,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -24203,7 +24239,11 @@
           <t>Shares issued for private placement 13</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -25004,7 +25044,11 @@
           <t>Proceeds from sale of marketable securities 7</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -25182,7 +25226,11 @@
           <t>Shares issued for private placement 13</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -26543,7 +26591,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -28377,7 +28429,11 @@
           <t>Shares issued for private placement 14</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -34045,7 +34101,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -35438,7 +35498,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -36174,7 +36238,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>-0.000201</v>
       </c>
@@ -36989,7 +37057,11 @@
           <t>Directors fees 15</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -38318,7 +38390,11 @@
           <t>Directors fees 13</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -40201,7 +40277,11 @@
           <t>Directors fees 16</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -41184,7 +41264,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
